--- a/outputs/32562.xlsx
+++ b/outputs/32562.xlsx
@@ -319,7 +319,7 @@
         <v>86</v>
       </c>
       <c r="B2" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A2,A2)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A2)</f>
         <v>1</v>
       </c>
     </row>
@@ -328,7 +328,7 @@
         <v>503</v>
       </c>
       <c r="B3" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A3,A3)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A3)</f>
         <v>1</v>
       </c>
     </row>
@@ -337,7 +337,7 @@
         <v>142</v>
       </c>
       <c r="B4" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A4,A4)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A4)</f>
         <v>1</v>
       </c>
     </row>
@@ -346,7 +346,7 @@
         <v>216</v>
       </c>
       <c r="B5" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A5,A5)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A5)</f>
         <v>1</v>
       </c>
     </row>
@@ -355,7 +355,7 @@
         <v>125</v>
       </c>
       <c r="B6" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A6,A6)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A6)</f>
         <v>1</v>
       </c>
     </row>
@@ -364,7 +364,7 @@
         <v>173</v>
       </c>
       <c r="B7" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A7,A7)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A7)</f>
         <v>1</v>
       </c>
     </row>
@@ -373,7 +373,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A8,A8)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A8)</f>
         <v>1</v>
       </c>
     </row>
@@ -382,7 +382,7 @@
         <v>434</v>
       </c>
       <c r="B9" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A9,A9)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A9)</f>
         <v>1</v>
       </c>
     </row>
@@ -391,7 +391,7 @@
         <v>627</v>
       </c>
       <c r="B10" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A10,A10)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A10)</f>
         <v>1</v>
       </c>
     </row>
@@ -400,7 +400,7 @@
         <v>377</v>
       </c>
       <c r="B11" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A11,A11)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A11)</f>
         <v>1</v>
       </c>
     </row>
@@ -409,7 +409,7 @@
         <v>508</v>
       </c>
       <c r="B12" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A12,A12)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A12)</f>
         <v>1</v>
       </c>
     </row>
@@ -418,8 +418,8 @@
         <v>374</v>
       </c>
       <c r="B13" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A13,A13)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($A$2:$A$21,A13)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -427,8 +427,8 @@
         <v>374</v>
       </c>
       <c r="B14" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A14,A14)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($A$2:$A$21,A14)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -436,7 +436,7 @@
         <v>374</v>
       </c>
       <c r="B15" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A15,A15)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A15)</f>
         <v>3</v>
       </c>
     </row>
@@ -445,8 +445,8 @@
         <v>321</v>
       </c>
       <c r="B16" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A16,A16)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($A$2:$A$21,A16)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -454,8 +454,8 @@
         <v>321</v>
       </c>
       <c r="B17" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A17,A17)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($A$2:$A$21,A17)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -463,7 +463,7 @@
         <v>321</v>
       </c>
       <c r="B18" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A18,A18)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A18)</f>
         <v>3</v>
       </c>
     </row>
@@ -472,7 +472,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A19,A19)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A19)</f>
         <v>1</v>
       </c>
     </row>
@@ -481,7 +481,7 @@
         <v>141</v>
       </c>
       <c r="B20" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A20,A20)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A20)</f>
         <v>1</v>
       </c>
     </row>
@@ -490,7 +490,7 @@
         <v>109</v>
       </c>
       <c r="B21" s="2" t="n">
-        <f aca="false">COUNTIF($A$2:A21,A21)</f>
+        <f aca="false">COUNTIF($A$2:$A$21,A21)</f>
         <v>1</v>
       </c>
     </row>
